--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:56</t>
+    <t xml:space="preserve">2026-09-09 22:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:46</t>
+    <t xml:space="preserve">2026-09-18 10:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:07</t>
+    <t xml:space="preserve">2026-09-23 12:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:12</t>
+    <t xml:space="preserve">2026-10-02 13:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Cañete</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Talcahuano</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:48</t>
+    <t xml:space="preserve">2026-10-04 08:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:31</t>
+    <t xml:space="preserve">2026-10-05 09:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
